--- a/static/search_results_4.xlsx
+++ b/static/search_results_4.xlsx
@@ -491,106 +491,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-10 08:01:09</t>
+          <t>2026-07-13 09:44:08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kandy</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IT Companies</t>
+          <t>Clothing Shops</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ontech IT Solutions: Software Company Sri Lanka</t>
+          <t>Urban Outfitters</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>, No 273/A/2, 1 william Gopallawa Road, Kandy 20000, Sri Lanka</t>
+          <t>, Roßmarkt 13, 60311 Frankfurt am Main-Innenstadt I, Germany</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+94 77 251 3161</t>
+          <t>+49 69 50954020</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>http://www.ontechsl.com/</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>contact@ontechsl.com</t>
-        </is>
-      </c>
+          <t>https://www.urbanoutfitters.com/de-de/</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-10 08:01:09</t>
+          <t>2026-07-13 09:44:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kandy</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IT Companies</t>
+          <t>Clothing Shops</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CircleBit (PVT) LTD</t>
+          <t>Primark</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>, No 112 Dharmashoka Mawatha, Kandy 20000, Sri Lanka</t>
+          <t>, Zeil 94, 60313 Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>+94 72 600 0000</t>
+          <t>+49 69 29723556</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://circlebit.net/</t>
+          <t>https://www.primark.com/de-de/stores/frankfurt/zeil-94?y_source=1_ODU3OTM2My03MTUtbG9jYXRpb24ud2Vic2l0ZQ%3D%3D</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -599,111 +595,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10 08:01:09</t>
+          <t>2026-07-13 09:44:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kandy</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IT Companies</t>
+          <t>Clothing Shops</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Soft-Master Technologies (Pvt) Ltd</t>
+          <t>COS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>, No:07 George E De Silva Mawatha, Kandy 20000, Sri Lanka</t>
+          <t>, Goethepl. 4, 60311 Frankfurt am Main-Innenstadt I, Germany</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+94 812 204 130</t>
+          <t>+49 69 13383680</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>http://softmaster.lk/</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>info@softmastergroup.com</t>
-        </is>
-      </c>
+          <t>http://www.cos.com/?utm_source=google_location&amp;utm_medium=organic&amp;utm_campaign=DE0580</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10 08:01:09</t>
+          <t>2026-07-13 09:44:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kandy</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IT Companies</t>
+          <t>Clothing Shops</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Introps IT</t>
+          <t>Frida</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>, 54 A Katugastota Rd, Kandy 20000, Sri Lanka</t>
+          <t>, Bleidenstraße 11, 60311 Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+94 71 150 0200</t>
+          <t>+49 69 56997407</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://introps.com/</t>
+          <t>http://www.frida-frankfurt.de/</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>info@introps.com</t>
+          <t>info@frida-frankfurt.de</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -711,217 +703,217 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10 08:01:09</t>
+          <t>2026-07-13 09:44:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kandy</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IT Companies</t>
+          <t>Clothing Shops</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Glenzsoft (Pvt.) Ltd</t>
+          <t>Shaping New Tomorrow Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>, 191/44 Srimath Kudarathwatta Mawatha, Kandy 20000, Sri Lanka</t>
+          <t>, Roßmarkt 15, 60311 Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+94 812 232 752</t>
+          <t>+49 40 74305535</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>http://glenzsoft.com/</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>https://shapingnewtomorrow.de/</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>help@shapingnewtomorrow.com</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10 08:01:09</t>
+          <t>2026-07-13 09:44:08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kandy</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IT Companies</t>
+          <t>Clothing Shops</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASN IT</t>
+          <t>ReSales Frankfurt am Main</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>, 1st Floor, 308 A/1/1 Katugastota Rd, Kandy, Sri Lanka</t>
+          <t>, Elisabethenstraße 14, 60594 Frankfurt-Süd, Germany</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+94 812 081 281</t>
+          <t>+49 3644 534472</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://asnit.lk/</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>support@asnit.lk</t>
-        </is>
-      </c>
+          <t>https://www.resales.de/</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10 08:01:09</t>
+          <t>2026-07-13 09:44:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kandy</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IT Companies</t>
+          <t>Clothing Shops</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avenir IT (Pvt) Ltd</t>
+          <t>Amora Mode</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>, 17/A Pitakanda Rd, Kandy 20000, Sri Lanka</t>
+          <t>, Große Eschenheimer Str. 7, 60313 Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+94 812 211 162</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>http://www.avenir.lk/</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>info@avenir.lk</t>
-        </is>
-      </c>
+          <t>+49 69 281570</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10 08:01:09</t>
+          <t>2026-07-13 09:44:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kandy</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IT Companies</t>
+          <t>Clothing Shops</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lashura Global</t>
+          <t>Carhartt WIP Store Frankfurt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>, No.65/1A Hewaheta Rd, Kandy 20000, Sri Lanka</t>
+          <t>, Neue Kräme 26, 60311 Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+94 78 292 0885</t>
+          <t>+49 69 21089894</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://www.lashuraglobal.com/</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>https://www.carhartt-wip.com/</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>info@carhartt-wip.com</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
